--- a/demo/reporte_detalle.xlsx
+++ b/demo/reporte_detalle.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="43">
   <si>
-    <t>Reporte de Ventas Q1 2026 â Detalle por Vendedor</t>
+    <t>Reporte de Ventas Q1 2026 — Detalle por Vendedor</t>
   </si>
   <si>
     <t>activo</t>
@@ -85,19 +85,19 @@
     <t>CRM Pro</t>
   </si>
   <si>
-    <t>Francisco RÃ­os</t>
+    <t>Francisco Ríos</t>
   </si>
   <si>
     <t>DevOps Tools</t>
   </si>
   <si>
-    <t>Ana GarcÃ­a</t>
+    <t>Ana García</t>
   </si>
   <si>
     <t>Norte</t>
   </si>
   <si>
-    <t>Marta LÃ³pez</t>
+    <t>Marta López</t>
   </si>
   <si>
     <t>Isabel Torres</t>
@@ -106,13 +106,13 @@
     <t>Roberto Silva</t>
   </si>
   <si>
-    <t>AndrÃ©s Reyes</t>
-  </si>
-  <si>
-    <t>HÃ©ctor Romero</t>
-  </si>
-  <si>
-    <t>Elena DÃ­az</t>
+    <t>Andrés Reyes</t>
+  </si>
+  <si>
+    <t>Héctor Romero</t>
+  </si>
+  <si>
+    <t>Elena Díaz</t>
   </si>
   <si>
     <t>Oeste</t>
@@ -127,19 +127,19 @@
     <t>Valentina Cruz</t>
   </si>
   <si>
-    <t>Luis MartÃ­nez</t>
+    <t>Luis Martínez</t>
   </si>
   <si>
     <t>Sur</t>
   </si>
   <si>
-    <t>Pedro SÃ¡nchez</t>
+    <t>Pedro Sánchez</t>
   </si>
   <si>
     <t>Carmen Medina</t>
   </si>
   <si>
-    <t>SofÃ­a Vargas</t>
+    <t>Sofía Vargas</t>
   </si>
   <si>
     <t>Adriana Ponce</t>
@@ -638,7 +638,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>98.66666666666667</v>
+        <v>98.7</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="3">
-        <v>71.66666666666667</v>
+        <v>71.7</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
@@ -702,7 +702,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="3">
-        <v>89.23076923076923</v>
+        <v>89.2</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -734,7 +734,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3">
-        <v>111.76470588235294</v>
+        <v>111.8</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -766,7 +766,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3">
-        <v>107.36842105263158</v>
+        <v>107.4</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="3">
-        <v>106.25</v>
+        <v>106.3</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -830,7 +830,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="3">
-        <v>107.05882352941177</v>
+        <v>107.1</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="3">
-        <v>95.71428571428571</v>
+        <v>95.7</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="B12" s="3">
-        <v>89.0909090909091</v>
+        <v>89.1</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -958,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="3">
-        <v>106.94444444444444</v>
+        <v>106.9</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="3">
-        <v>122.22222222222223</v>
+        <v>122.2</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -1022,7 +1022,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="3">
-        <v>109.0909090909091</v>
+        <v>109.1</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -1054,7 +1054,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="3">
-        <v>102.85714285714286</v>
+        <v>102.9</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -1086,7 +1086,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="3">
-        <v>92.6470588235294</v>
+        <v>92.6</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -1118,7 +1118,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="3">
-        <v>88.57142857142857</v>
+        <v>88.6</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -1150,7 +1150,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="3">
-        <v>84.61538461538461</v>
+        <v>84.6</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -1182,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="3">
-        <v>103.84615384615384</v>
+        <v>103.8</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="B22" s="3">
-        <v>70.6896551724138</v>
+        <v>70.7</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
